--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118765513</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
+        <v>97828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,673 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129885868</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98782</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>693783</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6385185</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129885832</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105942</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>693779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6385184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>30-tal</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129885237</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98765</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>693794</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6385169</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129885833</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105942</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>671</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>693797</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6385174</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129886459</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98672</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>693842</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6385113</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 plantor i vägkant</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129885118</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98755</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>693838</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6385104</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 planta</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>129885868</v>
       </c>
       <c r="B3" t="n">
-        <v>98782</v>
+        <v>98792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129885832</v>
       </c>
       <c r="B4" t="n">
-        <v>105942</v>
+        <v>105952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98765</v>
+        <v>98775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105942</v>
+        <v>105952</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98672</v>
+        <v>98682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98755</v>
+        <v>98765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,6 +1454,235 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129884441</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109652</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>693781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6385186</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129884748</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104273</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tofta-Visby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>693847</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6385122</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885868</v>
+        <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>98792</v>
+        <v>105956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693783</v>
+        <v>693779</v>
       </c>
       <c r="R3" t="n">
-        <v>6385185</v>
+        <v>6385184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885832</v>
+        <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>105952</v>
+        <v>98796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693779</v>
+        <v>693783</v>
       </c>
       <c r="R4" t="n">
-        <v>6385184</v>
+        <v>6385185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98775</v>
+        <v>98779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105952</v>
+        <v>105956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98682</v>
+        <v>98686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98765</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109652</v>
+        <v>109656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104273</v>
+        <v>104277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>105956</v>
+        <v>105959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>98796</v>
+        <v>98799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98779</v>
+        <v>98782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105956</v>
+        <v>105959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98686</v>
+        <v>98689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109656</v>
+        <v>109659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104277</v>
+        <v>104280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>105959</v>
+        <v>105960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>98799</v>
+        <v>98800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98782</v>
+        <v>98783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105959</v>
+        <v>105960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98689</v>
+        <v>98690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98772</v>
+        <v>98773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109659</v>
+        <v>109660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104280</v>
+        <v>104281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>105960</v>
+        <v>105977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>98800</v>
+        <v>98817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98783</v>
+        <v>98800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105960</v>
+        <v>105977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98690</v>
+        <v>98707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98773</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109660</v>
+        <v>109677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104281</v>
+        <v>104298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885868</v>
+        <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>105993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693783</v>
+        <v>693779</v>
       </c>
       <c r="R3" t="n">
-        <v>6385185</v>
+        <v>6385184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885832</v>
+        <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>105993</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693779</v>
+        <v>693783</v>
       </c>
       <c r="R4" t="n">
-        <v>6385184</v>
+        <v>6385185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885832</v>
+        <v>129885868</v>
       </c>
       <c r="B3" t="n">
-        <v>105993</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>671</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693779</v>
+        <v>693783</v>
       </c>
       <c r="R3" t="n">
-        <v>6385184</v>
+        <v>6385185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885868</v>
+        <v>129885832</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>105993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693783</v>
+        <v>693779</v>
       </c>
       <c r="R4" t="n">
-        <v>6385185</v>
+        <v>6385184</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885868</v>
+        <v>129885832</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>105996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693783</v>
+        <v>693779</v>
       </c>
       <c r="R3" t="n">
-        <v>6385185</v>
+        <v>6385184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885832</v>
+        <v>129885868</v>
       </c>
       <c r="B4" t="n">
-        <v>105993</v>
+        <v>98835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693779</v>
+        <v>693783</v>
       </c>
       <c r="R4" t="n">
-        <v>6385184</v>
+        <v>6385185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98816</v>
+        <v>98818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105993</v>
+        <v>105996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98723</v>
+        <v>98725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98806</v>
+        <v>98808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109693</v>
+        <v>109696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104314</v>
+        <v>104316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885832</v>
+        <v>129885868</v>
       </c>
       <c r="B3" t="n">
-        <v>105996</v>
+        <v>98922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>671</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693779</v>
+        <v>693783</v>
       </c>
       <c r="R3" t="n">
-        <v>6385184</v>
+        <v>6385185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885868</v>
+        <v>129885832</v>
       </c>
       <c r="B4" t="n">
-        <v>98835</v>
+        <v>106083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693783</v>
+        <v>693779</v>
       </c>
       <c r="R4" t="n">
-        <v>6385185</v>
+        <v>6385184</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
         <v>129885237</v>
       </c>
       <c r="B5" t="n">
-        <v>98818</v>
+        <v>98905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129885833</v>
       </c>
       <c r="B6" t="n">
-        <v>105996</v>
+        <v>106083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129886459</v>
       </c>
       <c r="B7" t="n">
-        <v>98725</v>
+        <v>98812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>129885118</v>
       </c>
       <c r="B8" t="n">
-        <v>98808</v>
+        <v>98895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>129884441</v>
       </c>
       <c r="B9" t="n">
-        <v>109696</v>
+        <v>109783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129884748</v>
       </c>
       <c r="B10" t="n">
-        <v>104316</v>
+        <v>104403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129885868</v>
+        <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>98835</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -943,7 +943,7 @@
         <v>6385185</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,19 +970,9 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,17 +992,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129885237</v>
+        <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>98818</v>
+        <v>99016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1030,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1050,7 +1040,7 @@
         <v>6385169</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,19 +1067,9 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1233,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129886459</v>
+        <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98725</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1244,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1274,7 +1254,7 @@
         <v>6385113</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,19 +1281,9 @@
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>07:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1345,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129885118</v>
+        <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>98808</v>
+        <v>99006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1346,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1386,7 +1356,7 @@
         <v>6385104</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,19 +1383,9 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1457,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129884441</v>
+        <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109783</v>
+        <v>109997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1452,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1502,7 +1462,7 @@
         <v>6385186</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,19 +1489,9 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129884748</v>
+        <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104403</v>
+        <v>104553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,13 +1548,9 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1614,7 +1560,7 @@
         <v>6385122</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,21 +1587,11 @@
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>07:09</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>07:09</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>Vägkant</t>
@@ -1667,7 +1603,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1683,6 +1618,205 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131599501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98948</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>693797</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6385174</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131598578</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98948</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>693779</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6385184</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>30-tal</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99006</v>
+        <v>99008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104553</v>
+        <v>104555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98948</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98948</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99008</v>
+        <v>99009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104555</v>
+        <v>104556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99036</v>
+        <v>99037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99019</v>
+        <v>99020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98926</v>
+        <v>98927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99009</v>
+        <v>99010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104556</v>
+        <v>104557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98951</v>
+        <v>98952</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98952</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99037</v>
+        <v>99040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99020</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98927</v>
+        <v>98930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99010</v>
+        <v>99013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104557</v>
+        <v>104555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98952</v>
+        <v>98955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98952</v>
+        <v>98955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104555</v>
+        <v>104556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99040</v>
+        <v>99046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98930</v>
+        <v>98936</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99013</v>
+        <v>99019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104556</v>
+        <v>104562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98955</v>
+        <v>98961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98955</v>
+        <v>98961</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99046</v>
+        <v>99049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99029</v>
+        <v>99032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98936</v>
+        <v>98939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99019</v>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104562</v>
+        <v>104566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98961</v>
+        <v>98964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98961</v>
+        <v>98964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>131599514</v>
       </c>
       <c r="B4" t="n">
-        <v>99049</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131598377</v>
       </c>
       <c r="B5" t="n">
-        <v>99032</v>
+        <v>99037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131597945</v>
       </c>
       <c r="B7" t="n">
-        <v>98939</v>
+        <v>98944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131598302</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>99027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131598891</v>
       </c>
       <c r="B9" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131598181</v>
       </c>
       <c r="B10" t="n">
-        <v>104566</v>
+        <v>104571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131599501</v>
       </c>
       <c r="B11" t="n">
-        <v>98964</v>
+        <v>98969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98964</v>
+        <v>98969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118765513</v>
+        <v>131599452</v>
       </c>
       <c r="B2" t="n">
-        <v>97833</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219797</v>
+        <v>671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkumla, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693839</v>
+        <v>693749</v>
       </c>
       <c r="R2" t="n">
-        <v>6385108</v>
+        <v>6385264</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,26 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Sofie Alveteg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129885832</v>
+        <v>131599453</v>
       </c>
       <c r="B3" t="n">
-        <v>105996</v>
+        <v>106421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,17 +808,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693779</v>
+        <v>693752</v>
       </c>
       <c r="R3" t="n">
-        <v>6385184</v>
+        <v>6385271</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30-tal</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,39 +872,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131599514</v>
+        <v>131599454</v>
       </c>
       <c r="B4" t="n">
-        <v>99056</v>
+        <v>106421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693783</v>
+        <v>693769</v>
       </c>
       <c r="R4" t="n">
-        <v>6385185</v>
+        <v>6385269</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,12 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131598377</v>
+        <v>131599455</v>
       </c>
       <c r="B5" t="n">
-        <v>99039</v>
+        <v>106421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693794</v>
+        <v>693770</v>
       </c>
       <c r="R5" t="n">
-        <v>6385169</v>
+        <v>6385279</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,17 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fåtalig</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129885833</v>
+        <v>131599456</v>
       </c>
       <c r="B6" t="n">
-        <v>105996</v>
+        <v>106421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,23 +1112,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693797</v>
+        <v>693779</v>
       </c>
       <c r="R6" t="n">
-        <v>6385174</v>
+        <v>6385282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,22 +1148,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131597945</v>
+        <v>131599457</v>
       </c>
       <c r="B7" t="n">
-        <v>98946</v>
+        <v>106421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219769</v>
+        <v>671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693842</v>
+        <v>693775</v>
       </c>
       <c r="R7" t="n">
-        <v>6385113</v>
+        <v>6385292</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,17 +1250,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 plantor i vägkant</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,39 +1280,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131598302</v>
+        <v>131599458</v>
       </c>
       <c r="B8" t="n">
-        <v>99029</v>
+        <v>106421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219797</v>
+        <v>671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693838</v>
+        <v>693789</v>
       </c>
       <c r="R8" t="n">
-        <v>6385104</v>
+        <v>6385298</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1380,17 +1352,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,56 +1382,52 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131598891</v>
+        <v>131598647</v>
       </c>
       <c r="B9" t="n">
-        <v>110012</v>
+        <v>45050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>102018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693781</v>
+        <v>693870</v>
       </c>
       <c r="R9" t="n">
-        <v>6385186</v>
+        <v>6385141</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1486,12 +1454,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På rödklint 2 ex åkervädd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1473,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1512,55 +1484,72 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Mikael Molander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131598181</v>
+        <v>121104892</v>
       </c>
       <c r="B10" t="n">
-        <v>104574</v>
+        <v>45300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220164</v>
+        <v>102918</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gotland (västra), Gtl</t>
+          <t>Storvätskogen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693847</v>
+        <v>693760</v>
       </c>
       <c r="R10" t="n">
-        <v>6385122</v>
+        <v>6385201</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,17 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,28 +1587,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sofie Alveteg</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131599501</v>
+        <v>131597945</v>
       </c>
       <c r="B11" t="n">
-        <v>98971</v>
+        <v>99087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>219769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693797</v>
+        <v>693842</v>
       </c>
       <c r="R11" t="n">
-        <v>6385174</v>
+        <v>6385113</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1686,12 +1671,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 plantor i vägkant</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,7 +1701,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Mikael Molander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1721,7 +1711,7 @@
         <v>131598578</v>
       </c>
       <c r="B12" t="n">
-        <v>98971</v>
+        <v>99112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,6 +1807,1837 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131599501</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>693797</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6385174</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118765513</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>693839</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6385108</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131598301</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>693763</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6385178</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Några</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131598302</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>693838</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6385104</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 planta</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131599001</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>693824</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6385057</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kant av väg</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131598377</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>693794</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6385169</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131598605</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>693754</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6385179</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 plantor</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131598611</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>693866</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6385127</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131598612</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>693877</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6385145</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 plntor</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131598614</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>693921</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6385218</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131599514</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>693783</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6385185</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131598828</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>693773</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6385264</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118765523</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>693874</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6385129</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118765524</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>693848</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6385107</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131598181</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104719</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>693847</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6385122</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131598020</v>
+      </c>
+      <c r="B28" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>693853</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6385082</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spridd</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131598891</v>
+      </c>
+      <c r="B29" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>693781</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6385186</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131597939</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>693885</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6385140</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Västerhejde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3 plantor</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27168-2022 artfynd.xlsx
+++ b/artfynd/A 27168-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599454</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599456</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599458</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598647</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121104892</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131597945</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598578</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599501</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765513</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598301</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598302</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599001</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598377</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598605</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598611</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2728,6 +2828,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598612</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2830,6 +2935,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598614</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2927,6 +3037,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131599514</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,6 +3139,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598828</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765523</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3234,6 +3359,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765524</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3336,6 +3466,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598181</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3438,6 +3573,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598020</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598891</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3638,8 +3783,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131597939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>